--- a/outputs/reports/stacked_ensemble/feature_importance_top10.xlsx
+++ b/outputs/reports/stacked_ensemble/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1703765778033789</v>
+        <v>0.1027335695024538</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01773032250328394</v>
+        <v>0.006969778495202472</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.04%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1219556905672209</v>
+        <v>0.09652091154231966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01269137901902762</v>
+        <v>0.006548291633037551</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=12.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.08969255748179694</v>
+        <v>0.07809443240098939</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009333900180409971</v>
+        <v>0.005298179535467795</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=8.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.07269679987429753</v>
+        <v>0.06968751652302239</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00756522829220968</v>
+        <v>0.00472782710070857</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=7.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05321321950452901</v>
+        <v>0.05950933220535835</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005537659902654923</v>
+        <v>0.004037306071204505</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=5.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05130152411878593</v>
+        <v>0.05448633215248471</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005338718380561547</v>
+        <v>0.003696529459241427</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.13%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LBST_EXE_SUM_AMT</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>인건비집행합계금액</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04928507830094729</v>
+        <v>0.04909321630624239</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005128875953147982</v>
+        <v>0.003330642991660082</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비집행합계금액(LBST_EXE_SUM_AMT). 기여도(정규화 비중)=4.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04705913161891651</v>
+        <v>0.04446676888912223</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00489723171509393</v>
+        <v>0.003016769796430951</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.04588068925784221</v>
+        <v>0.03666790038597665</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00477459653024187</v>
+        <v>0.002487669267330406</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.59%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>보조금전용신용카드집행건수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.04224061174252269</v>
+        <v>0.0365357161740591</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004395790070365391</v>
+        <v>0.002478701461752442</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.22%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
